--- a/data/trans_camb/P15B_tráfico-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P15B_tráfico-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-26,17</t>
+          <t>-37,31</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,17</t>
+          <t>26,16</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,27</t>
+          <t>-6,08</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-27,8; 14,82</t>
+          <t>-27,54; 16,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-45,15; -2,38</t>
+          <t>-43,89; -1,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-58,25; 28,3</t>
+          <t>-59,38; 11,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-36,87; 30,92</t>
+          <t>-36,1; 33,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-45,35; 24,63</t>
+          <t>-43,96; 28,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,61; 62,06</t>
+          <t>-19,78; 61,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-23,84; 12,27</t>
+          <t>-24,77; 12,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-37,75; -0,66</t>
+          <t>-37,65; 0,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-28,37; 29,58</t>
+          <t>-32,74; 21,55</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-51,16%</t>
+          <t>-72,93%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>-12,26%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-43,67; 41,44</t>
+          <t>-43,61; 46,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-71,33; -3,91</t>
+          <t>-69,59; 2,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 71,94</t>
+          <t>-100,0; 44,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-53,56; 160,75</t>
+          <t>-54,04; 211,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-68,11; 126,43</t>
+          <t>-71,6; 153,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-27,66; 307,59</t>
+          <t>-32,41; 283,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,32; 32,7</t>
+          <t>-39,49; 32,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-62,07; 0,39</t>
+          <t>-63,08; 0,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-49,39; 79,93</t>
+          <t>-60,37; 52,68</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16,0</t>
+          <t>12,07</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-12,33</t>
+          <t>-13,46</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,98</t>
+          <t>3,93</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-23,87; 11,84</t>
+          <t>-25,75; 11,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-24,94; 15,22</t>
+          <t>-24,75; 16,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,59; 45,87</t>
+          <t>-16,4; 41,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-26,06; 25,77</t>
+          <t>-29,67; 25,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-24,45; 33,63</t>
+          <t>-25,11; 35,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-39,66; 18,71</t>
+          <t>-42,34; 18,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-20,3; 10,68</t>
+          <t>-22,05; 9,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-19,89; 14,72</t>
+          <t>-19,67; 16,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-16,22; 31,13</t>
+          <t>-17,28; 24,75</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-37,13%</t>
+          <t>-40,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>12,42%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-56,56; 72,74</t>
+          <t>-56,87; 74,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-60,65; 79,11</t>
+          <t>-59,53; 91,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-46,46; 242,01</t>
+          <t>-44,91; 212,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-55,89; 187,1</t>
+          <t>-59,88; 170,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-51,25; 217,5</t>
+          <t>-53,53; 207,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-87,51; 170,68</t>
+          <t>-95,63; 134,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-48,58; 50,16</t>
+          <t>-51,87; 45,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,6; 70,91</t>
+          <t>-47,51; 80,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-44,24; 139,25</t>
+          <t>-48,17; 111,69</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15,77</t>
+          <t>17,16</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,19</t>
+          <t>13,68</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15,82</t>
+          <t>15,53</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,52; 30,63</t>
+          <t>-17,94; 30,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-19,73; 29,58</t>
+          <t>-21,47; 28,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,26; 41,32</t>
+          <t>-15,36; 40,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-27,25; 24,9</t>
+          <t>-27,26; 24,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-29,67; 24,5</t>
+          <t>-32,02; 22,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 39,08</t>
+          <t>-17,57; 37,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 23,13</t>
+          <t>-12,68; 23,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-16,38; 18,59</t>
+          <t>-17,88; 19,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 34,34</t>
+          <t>-4,08; 33,4</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>74,94%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-50,35; 554,53</t>
+          <t>-54,34; 511,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-57,57; 610,39</t>
+          <t>-64,58; 584,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-34,79; —</t>
+          <t>-42,85; 745,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-70,29; —</t>
+          <t>-74,05; 406,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-83,5; —</t>
+          <t>-82,19; 397,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-35,73; 609,25</t>
+          <t>-45,63; 464,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-38,11; 330,67</t>
+          <t>-40,2; 241,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-54,0; 193,72</t>
+          <t>-55,47; 201,96</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 458,86</t>
+          <t>-17,21; 401,58</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11,27</t>
+          <t>14,6</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-26,01</t>
+          <t>-23,29</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,68</t>
+          <t>1,4</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-35,14; 8,54</t>
+          <t>-36,03; 8,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-33,09; 17,2</t>
+          <t>-35,1; 16,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,15; 31,0</t>
+          <t>-14,57; 34,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-56,56; 12,69</t>
+          <t>-59,46; 12,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-44,92; 32,16</t>
+          <t>-44,39; 31,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-58,77; 5,66</t>
+          <t>-58,61; 10,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-33,62; 6,55</t>
+          <t>-33,95; 6,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-26,57; 18,47</t>
+          <t>-24,99; 19,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-23,6; 16,11</t>
+          <t>-20,42; 20,12</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-67,65%</t>
+          <t>-60,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-7,09%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -1441,37 +1441,37 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-56,67; —</t>
+          <t>-46,66; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-87,73; 152,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-71,52; 259,19</t>
+          <t>-73,87; 277,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-90,4; 76,55</t>
+          <t>-87,16; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-84,32; 62,7</t>
+          <t>-83,87; 118,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-70,77; 202,22</t>
+          <t>-67,08; 239,4</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-60,99; 167,53</t>
+          <t>-53,18; 259,37</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>1,29</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,96</t>
+          <t>20,26</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>9,91</t>
+          <t>10,94</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-41,49; 24,94</t>
+          <t>-38,96; 26,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-34,96; 36,92</t>
+          <t>-33,92; 34,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-36,92; 24,91</t>
+          <t>-38,09; 24,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,8; 26,93</t>
+          <t>4,87; 26,64</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,82</t>
+          <t>0,0; 16,14</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,64; 32,22</t>
+          <t>10,92; 31,43</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-17,78; 17,12</t>
+          <t>-16,64; 17,03</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-21,2; 12,26</t>
+          <t>-19,38; 11,85</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 22,81</t>
+          <t>-9,14; 23,47</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>106,21%</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-78,0; —</t>
+          <t>-73,78; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-81,38; —</t>
+          <t>-77,36; —</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-46,95; —</t>
+          <t>-48,04; —</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-26,48</t>
+          <t>-19,69</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,35</t>
+          <t>3,27</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-6,73</t>
+          <t>-4,51</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-70,87; 23,06</t>
+          <t>-74,77; 27,01</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-81,82; 0,0</t>
+          <t>-81,89; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-75,41; 14,35</t>
+          <t>-72,08; 21,59</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-40,9; 11,57</t>
+          <t>-35,6; 11,71</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-40,17; 7,1</t>
+          <t>-43,75; 7,05</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-32,23; 18,45</t>
+          <t>-32,3; 18,45</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-39,04; 9,62</t>
+          <t>-34,07; 11,81</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-42,49; -0,3</t>
+          <t>-44,64; 0,0</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-33,56; 11,68</t>
+          <t>-33,78; 13,47</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-65,03%</t>
+          <t>-48,36%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-31,42%</t>
+          <t>-21,08%</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-95,08; —</t>
+          <t>-91,12; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
+          <t>-91,48; —</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-76,64; 181,36</t>
+          <t>-72,74; 227,88</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-28,46</t>
+          <t>-28,63</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-5,88</t>
+          <t>-5,82</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-68,88; 9,38</t>
+          <t>-62,83; 13,91</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-71,71; 5,51</t>
+          <t>-70,45; 5,58</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-75,97; 1,7</t>
+          <t>-82,42; 1,47</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-17,75; 7,48</t>
+          <t>-17,36; 6,15</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-16,53; 5,86</t>
+          <t>-18,57; 5,9</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-18,03; 6,92</t>
+          <t>-17,74; 7,18</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-21,09; 5,48</t>
+          <t>-21,55; 5,5</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-20,2; 3,3</t>
+          <t>-21,17; 3,75</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-20,8; 2,8</t>
+          <t>-21,12; 2,75</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-94,46%</t>
+          <t>-95,03%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-58,64%</t>
+          <t>-58,03%</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-94,76; 262,75</t>
+          <t>-99,42; —</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-92,77; —</t>
+          <t>-91,95; 206,51</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-5,58</t>
+          <t>-5,32</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,99</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-3,14</t>
+          <t>-3,0</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-17,71; 2,78</t>
+          <t>-17,21; 3,31</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-22,0; -0,53</t>
+          <t>-22,03; -0,65</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-16,66; 6,17</t>
+          <t>-16,81; 6,44</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 6,63</t>
+          <t>-12,59; 7,81</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-14,1; 5,34</t>
+          <t>-14,48; 5,47</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 10,99</t>
+          <t>-9,74; 10,45</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 1,56</t>
+          <t>-11,88; 2,37</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-15,49; -0,61</t>
+          <t>-15,56; -0,42</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 4,63</t>
+          <t>-11,54; 4,16</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-17,27%</t>
+          <t>-16,46%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-11,46%</t>
+          <t>-10,95%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-43,98; 14,76</t>
+          <t>-42,74; 13,74</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-57,0; -2,3</t>
+          <t>-55,57; -2,74</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-43,94; 22,92</t>
+          <t>-43,58; 25,03</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-42,84; 47,86</t>
+          <t>-43,35; 55,98</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-50,7; 39,07</t>
+          <t>-52,03; 35,72</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-37,16; 75,82</t>
+          <t>-35,03; 73,75</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-38,37; 7,78</t>
+          <t>-36,78; 11,36</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-48,46; -3,11</t>
+          <t>-47,54; -1,98</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-34,91; 21,38</t>
+          <t>-34,36; 18,67</t>
         </is>
       </c>
     </row>
